--- a/docs/data/jp/xlsx/6099.xlsx
+++ b/docs/data/jp/xlsx/6099.xlsx
@@ -7914,7 +7914,7 @@
     <row r="100">
       <c r="A100" s="20" t="inlineStr">
         <is>
-          <t>Consumption Tax Exemption Gain NOI</t>
+          <t>소비세 등 면제 이익</t>
         </is>
       </c>
       <c r="C100" s="22" t="n">
@@ -16624,7 +16624,7 @@
     <row r="129">
       <c r="A129" s="20" t="inlineStr">
         <is>
-          <t>Deposits Received From Employees</t>
+          <t>종업원 예수금</t>
         </is>
       </c>
       <c r="D129" s="22" t="n">
